--- a/data/trans_dic/IP16A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 45,74</t>
+          <t>20,21; 48,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,9; 51,92</t>
+          <t>26,36; 53,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 52,95</t>
+          <t>23,5; 52,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,17; 57,68</t>
+          <t>25,22; 54,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,4; 46,28</t>
+          <t>18,02; 45,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,07; 56,45</t>
+          <t>30,81; 55,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 40,13</t>
+          <t>12,56; 42,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,4; 43,67</t>
+          <t>15,31; 45,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,24; 41,75</t>
+          <t>22,01; 41,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,04; 49,6</t>
+          <t>31,29; 49,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 41,74</t>
+          <t>21,52; 41,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,29; 45,59</t>
+          <t>23,65; 45,29</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 37,35</t>
+          <t>15,22; 36,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,59; 58,26</t>
+          <t>36,71; 58,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,44; 46,87</t>
+          <t>26,36; 45,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 55,2</t>
+          <t>24,28; 55,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 62,42</t>
+          <t>35,18; 60,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,04; 46,3</t>
+          <t>24,1; 46,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,93; 51,58</t>
+          <t>29,08; 51,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,38; 57,37</t>
+          <t>35,5; 57,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,9; 45,62</t>
+          <t>28,92; 45,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,5; 49,27</t>
+          <t>34,11; 49,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,39; 44,98</t>
+          <t>30,14; 44,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,08; 53,39</t>
+          <t>34,48; 53,22</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 50,35</t>
+          <t>22,15; 51,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 52,48</t>
+          <t>28,28; 52,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,62; 54,21</t>
+          <t>28,7; 55,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,5; 62,06</t>
+          <t>13,18; 61,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,2; 58,85</t>
+          <t>32,17; 59,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,71; 50,66</t>
+          <t>28,87; 51,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,12; 58,95</t>
+          <t>31,95; 58,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,21; 58,68</t>
+          <t>32,96; 60,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,6; 50,97</t>
+          <t>30,34; 51,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,5; 48,78</t>
+          <t>32,08; 47,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,86; 52,55</t>
+          <t>33,35; 52,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,59; 55,17</t>
+          <t>23,51; 55,6</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,76; 60,86</t>
+          <t>27,44; 61,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,79; 52,3</t>
+          <t>29,44; 52,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,13; 54,43</t>
+          <t>30,42; 54,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 61,13</t>
+          <t>31,89; 61,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 53,67</t>
+          <t>26,16; 51,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,24; 50,75</t>
+          <t>27,83; 51,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,11; 48,35</t>
+          <t>22,93; 47,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 62,87</t>
+          <t>33,72; 63,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 50,91</t>
+          <t>31,23; 52,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,49; 49,53</t>
+          <t>32,32; 48,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,88; 48,65</t>
+          <t>29,98; 48,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,68; 57,45</t>
+          <t>37,36; 58,34</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,2; 40,04</t>
+          <t>25,9; 39,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,18; 47,32</t>
+          <t>36,17; 47,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,13; 45,07</t>
+          <t>32,81; 45,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,21; 50,31</t>
+          <t>24,32; 50,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,93; 47,9</t>
+          <t>34,86; 47,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,35; 45,05</t>
+          <t>33,53; 44,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,62; 44,17</t>
+          <t>30,69; 43,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,44; 50,87</t>
+          <t>37,46; 50,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,06; 42,15</t>
+          <t>32,53; 42,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,92</t>
+          <t>36,28; 44,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,52; 42,23</t>
+          <t>33,53; 42,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,13; 48,3</t>
+          <t>32,5; 47,98</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15547</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11823</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10452</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17005</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7768</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19260</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32552</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18457</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>18220</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6632; 15781</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10818; 21817</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7534; 16849</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6518; 14198</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5166; 12971</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12121; 21871</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3515; 11794</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4235; 12626</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>13537; 25329</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>25156; 39659</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12922; 25004</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>12651; 24232</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10553</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24842</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18997</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18045</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19929</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18301</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19969</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>29501</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30481</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>43144</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38966</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>47547</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6337; 15104</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19228; 30802</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14080; 24250</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10744; 24622</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14530; 25170</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12580; 24027</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>14471; 25864</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>22655; 36805</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>23989; 38020</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>35673; 51847</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>31103; 46209</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>37255; 57500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17504</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14015</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28899</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20340</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>26660</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>24640</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37844</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28381</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>55559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5575; 12990</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12284; 22944</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9742; 18673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10157; 47553</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11299; 20881</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14790; 26135</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10344; 18776</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18760; 34235</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>18289; 30781</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>30367; 45191</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22121; 34511</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>31506; 74495</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20818</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18336</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14120</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15037</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19552</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13184</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>26257</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40370</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31520</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>30287</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7046; 15863</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14952; 26622</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13335; 23770</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9745; 18808</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10156; 19887</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13900; 25709</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8544; 17868</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>11399; 21310</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20142; 33589</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>32555; 49188</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>24313; 39278</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>24048; 37553</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>41295</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>63172</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>100638</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>153910</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117324</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>32457; 49838</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>67876; 89891</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>53571; 73725</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43225; 89984</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>50167; 68950</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>64620; 86300</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>45230; 63813</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>68245; 92357</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>87583; 113508</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>138008; 171072</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>104160; 132584</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>116988; 172684</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 48,09</t>
+          <t>19,14; 46,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,36; 53,16</t>
+          <t>25,44; 52,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 52,55</t>
+          <t>22,36; 49,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,22; 54,94</t>
+          <t>26,99; 56,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,02; 45,24</t>
+          <t>18,33; 45,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 55,59</t>
+          <t>30,55; 58,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 42,15</t>
+          <t>11,09; 41,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 45,65</t>
+          <t>14,85; 44,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,01; 41,19</t>
+          <t>22,72; 41,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,29; 49,33</t>
+          <t>32,02; 49,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 41,64</t>
+          <t>21,17; 40,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,65; 45,29</t>
+          <t>23,71; 44,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 36,27</t>
+          <t>16,42; 37,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,71; 58,8</t>
+          <t>36,97; 58,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,36; 45,4</t>
+          <t>25,92; 46,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,28; 55,65</t>
+          <t>24,14; 53,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,18; 60,94</t>
+          <t>35,88; 60,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,1; 46,03</t>
+          <t>24,57; 46,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,08; 51,98</t>
+          <t>29,16; 51,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 57,68</t>
+          <t>34,31; 56,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,92; 45,83</t>
+          <t>28,44; 44,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,11; 49,58</t>
+          <t>33,04; 48,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,14; 44,79</t>
+          <t>30,59; 46,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,48; 53,22</t>
+          <t>34,79; 53,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 51,62</t>
+          <t>22,68; 51,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,28; 52,83</t>
+          <t>29,9; 53,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 55,0</t>
+          <t>27,73; 53,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 61,7</t>
+          <t>12,85; 62,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,17; 59,45</t>
+          <t>32,59; 59,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,87; 51,02</t>
+          <t>28,49; 50,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 58,0</t>
+          <t>29,82; 58,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,96; 60,14</t>
+          <t>33,73; 60,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,34; 51,06</t>
+          <t>30,2; 50,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,08; 47,74</t>
+          <t>32,73; 48,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,35; 52,04</t>
+          <t>33,47; 51,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,51; 55,6</t>
+          <t>20,57; 55,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 61,78</t>
+          <t>28,83; 60,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,44; 52,42</t>
+          <t>30,57; 52,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 54,23</t>
+          <t>29,99; 55,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 61,54</t>
+          <t>31,66; 61,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 51,23</t>
+          <t>26,3; 52,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,83; 51,48</t>
+          <t>28,2; 51,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,93; 47,94</t>
+          <t>22,68; 49,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,72; 63,03</t>
+          <t>32,84; 62,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,23; 52,08</t>
+          <t>30,48; 50,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,32; 48,83</t>
+          <t>31,55; 48,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,98; 48,43</t>
+          <t>30,53; 48,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,36; 58,34</t>
+          <t>36,57; 58,02</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,9; 39,77</t>
+          <t>26,9; 40,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,17; 47,91</t>
+          <t>35,84; 48,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,81; 45,16</t>
+          <t>32,48; 44,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,32; 50,63</t>
+          <t>24,68; 50,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,86; 47,91</t>
+          <t>35,37; 47,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 44,78</t>
+          <t>33,24; 45,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,69; 43,3</t>
+          <t>30,42; 43,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,46; 50,69</t>
+          <t>36,84; 50,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,53; 42,16</t>
+          <t>33,17; 42,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,28; 44,98</t>
+          <t>36,45; 45,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,53; 42,68</t>
+          <t>33,28; 42,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,5; 47,98</t>
+          <t>31,55; 47,77</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6632; 15781</t>
+          <t>6281; 15293</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10818; 21817</t>
+          <t>10439; 21434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7534; 16849</t>
+          <t>7169; 15923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6518; 14198</t>
+          <t>6974; 14512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5166; 12971</t>
+          <t>5257; 12968</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12121; 21871</t>
+          <t>12018; 22907</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3515; 11794</t>
+          <t>3103; 11672</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4235; 12626</t>
+          <t>4108; 12212</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13537; 25329</t>
+          <t>13972; 25619</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25156; 39659</t>
+          <t>25740; 40053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12922; 25004</t>
+          <t>12710; 24309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12651; 24232</t>
+          <t>12683; 23846</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6337; 15104</t>
+          <t>6839; 15489</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19228; 30802</t>
+          <t>19367; 30871</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14080; 24250</t>
+          <t>13847; 25048</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10744; 24622</t>
+          <t>10682; 23863</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14530; 25170</t>
+          <t>14819; 24885</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12580; 24027</t>
+          <t>12826; 24028</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14471; 25864</t>
+          <t>14511; 25765</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22655; 36805</t>
+          <t>21890; 36150</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23989; 38020</t>
+          <t>23595; 37049</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35673; 51847</t>
+          <t>34548; 51105</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31103; 46209</t>
+          <t>31559; 47529</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37255; 57500</t>
+          <t>37589; 57301</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5575; 12990</t>
+          <t>5707; 13030</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12284; 22944</t>
+          <t>12986; 23255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9742; 18673</t>
+          <t>9413; 18218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10157; 47553</t>
+          <t>9903; 48174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11299; 20881</t>
+          <t>11447; 20824</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14790; 26135</t>
+          <t>14595; 25844</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10344; 18776</t>
+          <t>9653; 19069</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18760; 34235</t>
+          <t>19199; 34248</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18289; 30781</t>
+          <t>18209; 30717</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30367; 45191</t>
+          <t>30979; 45923</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22121; 34511</t>
+          <t>22198; 34237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31506; 74495</t>
+          <t>27563; 74195</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7046; 15863</t>
+          <t>7402; 15557</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14952; 26622</t>
+          <t>15524; 26700</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13335; 23770</t>
+          <t>13145; 24407</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9745; 18808</t>
+          <t>9676; 18738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10156; 19887</t>
+          <t>10207; 20515</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13900; 25709</t>
+          <t>14085; 25800</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8544; 17868</t>
+          <t>8454; 18363</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11399; 21310</t>
+          <t>11104; 21095</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20142; 33589</t>
+          <t>19655; 32792</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32555; 49188</t>
+          <t>31781; 48693</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24313; 39278</t>
+          <t>24760; 39425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24048; 37553</t>
+          <t>23542; 37348</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32457; 49838</t>
+          <t>33713; 51225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67876; 89891</t>
+          <t>67251; 90680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53571; 73725</t>
+          <t>53029; 73357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43225; 89984</t>
+          <t>43856; 89860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50167; 68950</t>
+          <t>50907; 68801</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64620; 86300</t>
+          <t>64064; 87054</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45230; 63813</t>
+          <t>44835; 63534</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68245; 92357</t>
+          <t>67131; 91778</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87583; 113508</t>
+          <t>89310; 114590</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138008; 171072</t>
+          <t>138640; 172841</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104160; 132584</t>
+          <t>103391; 131952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>116988; 172684</t>
+          <t>113536; 171925</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30,21%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43,22%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>32,29%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,88%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>36,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40,45%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,14; 46,6</t>
+          <t>17,4; 46,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,44; 52,22</t>
+          <t>31,07; 56,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 49,66</t>
+          <t>12,51; 40,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,99; 56,16</t>
+          <t>15,8; 45,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 45,23</t>
+          <t>19,41; 45,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,55; 58,22</t>
+          <t>25,9; 51,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 41,72</t>
+          <t>24,06; 52,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 44,15</t>
+          <t>26,43; 59,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,72; 41,66</t>
+          <t>23,24; 41,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,02; 49,83</t>
+          <t>31,04; 49,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 40,49</t>
+          <t>21,7; 41,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 44,57</t>
+          <t>25,82; 47,93</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>25,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>47,42%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>35,56%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>40,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,13%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 37,19</t>
+          <t>36,66; 62,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,97; 58,93</t>
+          <t>25,04; 46,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,92; 46,89</t>
+          <t>28,93; 51,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,14; 53,94</t>
+          <t>34,85; 57,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,88; 60,25</t>
+          <t>16,26; 37,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,57; 46,04</t>
+          <t>36,59; 58,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,16; 51,78</t>
+          <t>25,44; 46,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 56,65</t>
+          <t>30,76; 58,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,44; 44,66</t>
+          <t>28,9; 45,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,04; 48,87</t>
+          <t>33,5; 49,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 46,07</t>
+          <t>30,39; 44,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,79; 53,03</t>
+          <t>36,69; 54,38</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39,71%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44,38%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>35,47%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40,3%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,5%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>44,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,38%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,68; 51,78</t>
+          <t>32,2; 58,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,9; 53,55</t>
+          <t>29,71; 50,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,73; 53,66</t>
+          <t>31,12; 58,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 62,51</t>
+          <t>30,24; 56,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,59; 59,29</t>
+          <t>20,88; 50,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,49; 50,45</t>
+          <t>29,83; 52,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,82; 58,9</t>
+          <t>28,62; 54,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,73; 60,17</t>
+          <t>42,4; 69,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,2; 50,95</t>
+          <t>30,6; 50,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,73; 48,51</t>
+          <t>32,5; 48,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,47; 51,62</t>
+          <t>33,86; 52,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,57; 55,37</t>
+          <t>41,09; 60,98</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>43,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>41,84%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,83; 60,59</t>
+          <t>27,6; 53,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 52,58</t>
+          <t>27,24; 50,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,99; 55,68</t>
+          <t>23,11; 48,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,66; 61,31</t>
+          <t>35,78; 64,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,3; 52,85</t>
+          <t>26,76; 60,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,2; 51,66</t>
+          <t>29,79; 52,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,68; 49,27</t>
+          <t>29,13; 54,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,84; 62,39</t>
+          <t>32,1; 62,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,48; 50,85</t>
+          <t>31,55; 50,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 48,34</t>
+          <t>32,49; 49,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 48,61</t>
+          <t>29,88; 48,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,57; 58,02</t>
+          <t>38,18; 58,72</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,9; 40,88</t>
+          <t>34,93; 47,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,84; 48,33</t>
+          <t>33,35; 45,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,48; 44,93</t>
+          <t>30,62; 44,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,68; 50,56</t>
+          <t>37,41; 51,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,37; 47,81</t>
+          <t>26,2; 40,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,24; 45,17</t>
+          <t>35,18; 47,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 43,11</t>
+          <t>33,13; 45,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,84; 50,37</t>
+          <t>42,06; 55,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,17; 42,56</t>
+          <t>33,06; 42,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,45; 45,44</t>
+          <t>36,21; 44,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 42,48</t>
+          <t>33,52; 42,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,55; 47,77</t>
+          <t>41,64; 50,97</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17005</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7248</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>10598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15547</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>11823</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10452</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8662</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17005</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6634</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18324</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6281; 15293</t>
+          <t>4989; 13272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10439; 21434</t>
+          <t>12226; 22213</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7169; 15923</t>
+          <t>3499; 11228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6974; 14512</t>
+          <t>3891; 11294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5257; 12968</t>
+          <t>6368; 15012</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12018; 22907</t>
+          <t>10632; 21309</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3103; 11672</t>
+          <t>7715; 16979</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4108; 12212</t>
+          <t>6954; 15526</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13972; 25619</t>
+          <t>14294; 25675</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25740; 40053</t>
+          <t>24950; 39873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12710; 24309</t>
+          <t>13026; 25065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12683; 23846</t>
+          <t>13150; 24408</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19929</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18301</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19969</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26400</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10553</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24842</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18997</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18045</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19929</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18301</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19969</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29501</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47547</t>
+          <t>42057</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6839; 15489</t>
+          <t>15141; 25784</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19367; 30871</t>
+          <t>13069; 24168</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13847; 25048</t>
+          <t>14398; 25667</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10682; 23863</t>
+          <t>19676; 32721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14819; 24885</t>
+          <t>6770; 15554</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12826; 24028</t>
+          <t>19169; 30516</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14511; 25765</t>
+          <t>13590; 25035</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21890; 36150</t>
+          <t>11114; 21124</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23595; 37049</t>
+          <t>23969; 37843</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34548; 51105</t>
+          <t>35032; 51528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31559; 47529</t>
+          <t>31356; 46405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37589; 57301</t>
+          <t>33968; 50354</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20340</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23200</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8925</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>17504</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>14015</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28899</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>15716</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20340</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14366</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>28896</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>52096</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5707; 13030</t>
+          <t>11308; 20669</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12986; 23255</t>
+          <t>15218; 25953</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9413; 18218</t>
+          <t>10076; 19086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9903; 48174</t>
+          <t>15833; 29589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11447; 20824</t>
+          <t>5255; 12669</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14595; 25844</t>
+          <t>12953; 22790</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9653; 19069</t>
+          <t>9715; 18403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19199; 34248</t>
+          <t>21551; 35161</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18209; 30717</t>
+          <t>18446; 30727</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30979; 45923</t>
+          <t>30767; 46171</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22198; 34237</t>
+          <t>22458; 34852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27563; 74195</t>
+          <t>42393; 62917</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15037</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19552</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13184</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15694</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20818</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>18336</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14120</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15037</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19552</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13184</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>29709</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7402; 15557</t>
+          <t>10713; 20833</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15524; 26700</t>
+          <t>13604; 25344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13145; 24407</t>
+          <t>8612; 18020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9676; 18738</t>
+          <t>11276; 20431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10207; 20515</t>
+          <t>6870; 15627</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14085; 25800</t>
+          <t>15128; 26558</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8454; 18363</t>
+          <t>12766; 23857</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11104; 21095</t>
+          <t>9542; 18483</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19655; 32792</t>
+          <t>20348; 32831</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31781; 48693</t>
+          <t>32730; 49893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24760; 39425</t>
+          <t>24232; 39456</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23542; 37348</t>
+          <t>23380; 35957</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>59343</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33713; 51225</t>
+          <t>50277; 68940</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67251; 90680</t>
+          <t>64263; 86818</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53029; 73357</t>
+          <t>45123; 65094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43856; 89860</t>
+          <t>61711; 84667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50907; 68801</t>
+          <t>32833; 50167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64064; 87054</t>
+          <t>66003; 88793</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44835; 63534</t>
+          <t>54080; 73578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67131; 91778</t>
+          <t>60145; 80004</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89310; 114590</t>
+          <t>89012; 113480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138640; 172841</t>
+          <t>137731; 170864</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103391; 131952</t>
+          <t>104113; 131183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113536; 171925</t>
+          <t>128241; 156954</t>
         </is>
       </c>
     </row>
